--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-08-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-08-2025.xlsx
@@ -591,27 +591,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -642,7 +642,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>£11.15 Pre Sale Price-£11.99</t>
+          <t>£10.98 Pre Sale Price-£11.99</t>
         </is>
       </c>
     </row>
@@ -712,27 +712,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -763,7 +763,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>£12.80 Pre Sale Price-£13.99</t>
+          <t>£12.33 Pre Sale Price-£13.99</t>
         </is>
       </c>
     </row>
@@ -833,27 +833,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -884,7 +884,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>£15.99 Pre Sale Price-£17.99</t>
+          <t>£15.75 Pre Sale Price-£17.99</t>
         </is>
       </c>
     </row>
@@ -954,27 +954,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>£16.70 Pre Sale Price-£19.99</t>
+          <t>£16.50 Pre Sale Price-£19.99</t>
         </is>
       </c>
     </row>
@@ -1075,27 +1075,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>£21.20 Pre Sale Price-£21.99</t>
+          <t>£21.00 Pre Sale Price-£21.99</t>
         </is>
       </c>
     </row>
@@ -1196,27 +1196,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>£23.99 Pre Sale Price-£24.99</t>
+          <t>£22.76 Pre Sale Price-£24.99</t>
         </is>
       </c>
     </row>
@@ -1317,27 +1317,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -1438,27 +1438,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>£26.99 Pre Sale Price-£27.99</t>
+          <t>£26.40 Pre Sale Price-£27.99</t>
         </is>
       </c>
     </row>
@@ -1559,27 +1559,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>£28.99 Pre Sale Price-£31.99</t>
+          <t>£28.80 Pre Sale Price-£31.99</t>
         </is>
       </c>
     </row>
@@ -1680,27 +1680,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>£28.61 Pre Sale Price-£32.99</t>
+          <t>£28.35 Pre Sale Price-£32.99</t>
         </is>
       </c>
     </row>
@@ -1801,27 +1801,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>£36.90 Pre Sale Price-£39.99</t>
+          <t>£36.50 Pre Sale Price-£39.99</t>
         </is>
       </c>
     </row>
@@ -1922,27 +1922,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>£35.09 Pre Sale Price-£37.99</t>
+          <t>£34.90 Pre Sale Price-£37.99</t>
         </is>
       </c>
     </row>
@@ -2043,27 +2043,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>£42.78 Pre Sale Price-£44.99</t>
+          <t>£42.50 Pre Sale Price-£44.99</t>
         </is>
       </c>
     </row>
@@ -2164,27 +2164,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -2285,27 +2285,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>£43.58 Pre Sale Price-£49.99</t>
+          <t>£43.50 Pre Sale Price-£49.99</t>
         </is>
       </c>
     </row>
@@ -2503,27 +2503,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -2624,27 +2624,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -2745,27 +2745,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -2866,27 +2866,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -2987,27 +2987,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -3108,27 +3108,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -3229,27 +3229,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -3350,27 +3350,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
@@ -3471,27 +3471,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d4fd6b25+79621]
-	GetHandleVerifier [0x0x7ff7d4fd6b80+79712]
-	(No symbol) [0x0x7ff7d4d6c0ea]
-	(No symbol) [0x0x7ff7d4dc2f56]
-	(No symbol) [0x0x7ff7d4dc320c]
-	(No symbol) [0x0x7ff7d4e165b7]
-	(No symbol) [0x0x7ff7d4deb17f]
-	(No symbol) [0x0x7ff7d4e133d0]
-	(No symbol) [0x0x7ff7d4deaf13]
-	(No symbol) [0x0x7ff7d4db4151]
-	(No symbol) [0x0x7ff7d4db4ee3]
-	GetHandleVerifier [0x0x7ff7d529683d+2962461]
-	GetHandleVerifier [0x0x7ff7d5290b5d+2938685]
-	GetHandleVerifier [0x0x7ff7d52af71d+3064573]
-	GetHandleVerifier [0x0x7ff7d4ff0c6e+186446]
-	GetHandleVerifier [0x0x7ff7d4ff8a3f+218655]
-	GetHandleVerifier [0x0x7ff7d4fdf914+115956]
-	GetHandleVerifier [0x0x7ff7d4fdfac9+116393]
-	GetHandleVerifier [0x0x7ff7d4fc5ef8+10968]
-	BaseThreadInitThunk [0x0x7ffbc8dee8d7+23]
-	RtlUserThreadStart [0x0x7ffbc9f5c34c+44]
+	GetHandleVerifier [0x0x7ff740186b25+79621]
+	GetHandleVerifier [0x0x7ff740186b80+79712]
+	(No symbol) [0x0x7ff73ff1c0ea]
+	(No symbol) [0x0x7ff73ff72f56]
+	(No symbol) [0x0x7ff73ff7320c]
+	(No symbol) [0x0x7ff73ffc65b7]
+	(No symbol) [0x0x7ff73ff9b17f]
+	(No symbol) [0x0x7ff73ffc33d0]
+	(No symbol) [0x0x7ff73ff9af13]
+	(No symbol) [0x0x7ff73ff64151]
+	(No symbol) [0x0x7ff73ff64ee3]
+	GetHandleVerifier [0x0x7ff74044683d+2962461]
+	GetHandleVerifier [0x0x7ff740440b5d+2938685]
+	GetHandleVerifier [0x0x7ff74045f71d+3064573]
+	GetHandleVerifier [0x0x7ff7401a0c6e+186446]
+	GetHandleVerifier [0x0x7ff7401a8a3f+218655]
+	GetHandleVerifier [0x0x7ff74018f914+115956]
+	GetHandleVerifier [0x0x7ff74018fac9+116393]
+	GetHandleVerifier [0x0x7ff740175ef8+10968]
+	BaseThreadInitThunk [0x0x7ff9a288e8d7+23]
+	RtlUserThreadStart [0x0x7ff9a473c34c+44]
 </t>
         </is>
       </c>
